--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>BIBS UAT environment (address issued with the passwords). Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -923,7 +923,7 @@
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS UAT environment (address issued with the passwords). Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
+          <t>Environment: BIBS UAT environment: https://uat.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>BIBS UAT environment (address issued with the passwords). Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS DEV environment: https://dev.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -923,7 +923,7 @@
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS UAT environment: https://uat.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
+          <t>Environment: BIBS DEV environment: https://dev.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS DEV environment: https://dev.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,13 +715,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -750,6 +753,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -822,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -889,6 +894,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -920,6 +926,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -927,6 +934,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -984,6 +992,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -952,7 +952,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1333,7 +1333,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2028,7 +2028,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3167,7 +3167,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3229,7 +3229,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_UAT_BRD-06_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -2026,7 +2026,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
